--- a/harmonized_tables_advp/from_41823034_table2_v1.xlsx
+++ b/harmonized_tables_advp/from_41823034_table2_v1.xlsx
@@ -703,7 +703,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ukbb + ros/map + dbgap + phs001672.v1.p1 + adsp</t>
+          <t>dbgap + phs001672.v1.p1 + ukbb + adsp + ros/map</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -713,19 +713,19 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1000g + 1000 genomes phase 3 + topmed</t>
+          <t>1000 genomes phase 3 + 1000g + topmed</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>european ancestry + aa + eur</t>
+          <t>eur + european ancestry + aa</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>depression + bipolar disorder + schizophrenia + alzheimers disease</t>
+          <t>bipolar disorder + schizophrenia + alzheimers disease + depression</t>
         </is>
       </c>
       <c r="W2" t="inlineStr"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ukbb + ros/map + dbgap + phs001672.v1.p1 + adsp</t>
+          <t>dbgap + phs001672.v1.p1 + ukbb + adsp + ros/map</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -832,19 +832,19 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1000g + 1000 genomes phase 3 + topmed</t>
+          <t>1000 genomes phase 3 + 1000g + topmed</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>european ancestry + aa + eur</t>
+          <t>eur + european ancestry + aa</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>depression + bipolar disorder + schizophrenia + alzheimers disease</t>
+          <t>bipolar disorder + schizophrenia + alzheimers disease + depression</t>
         </is>
       </c>
       <c r="W3" t="inlineStr"/>
@@ -941,7 +941,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ukbb + ros/map + dbgap + phs001672.v1.p1 + adsp</t>
+          <t>dbgap + phs001672.v1.p1 + ukbb + adsp + ros/map</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -951,19 +951,19 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1000g + 1000 genomes phase 3 + topmed</t>
+          <t>1000 genomes phase 3 + 1000g + topmed</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>european ancestry + aa + eur</t>
+          <t>eur + european ancestry + aa</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>depression + bipolar disorder + schizophrenia + alzheimers disease</t>
+          <t>bipolar disorder + schizophrenia + alzheimers disease + depression</t>
         </is>
       </c>
       <c r="W4" t="inlineStr"/>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ukbb + ros/map + dbgap + phs001672.v1.p1 + adsp</t>
+          <t>dbgap + phs001672.v1.p1 + ukbb + adsp + ros/map</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -1070,19 +1070,19 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1000g + 1000 genomes phase 3 + topmed</t>
+          <t>1000 genomes phase 3 + 1000g + topmed</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>european ancestry + aa + eur</t>
+          <t>eur + european ancestry + aa</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>depression + bipolar disorder + schizophrenia + alzheimers disease</t>
+          <t>bipolar disorder + schizophrenia + alzheimers disease + depression</t>
         </is>
       </c>
       <c r="W5" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ukbb + ros/map + dbgap + phs001672.v1.p1 + adsp</t>
+          <t>dbgap + phs001672.v1.p1 + ukbb + adsp + ros/map</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -1189,19 +1189,19 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1000g + 1000 genomes phase 3 + topmed</t>
+          <t>1000 genomes phase 3 + 1000g + topmed</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>european ancestry + aa + eur</t>
+          <t>eur + european ancestry + aa</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>depression + bipolar disorder + schizophrenia + alzheimers disease</t>
+          <t>bipolar disorder + schizophrenia + alzheimers disease + depression</t>
         </is>
       </c>
       <c r="W6" t="inlineStr"/>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ukbb + ros/map + dbgap + phs001672.v1.p1 + adsp</t>
+          <t>dbgap + phs001672.v1.p1 + ukbb + adsp + ros/map</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -1308,19 +1308,19 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1000g + 1000 genomes phase 3 + topmed</t>
+          <t>1000 genomes phase 3 + 1000g + topmed</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>european ancestry + aa + eur</t>
+          <t>eur + european ancestry + aa</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>depression + bipolar disorder + schizophrenia + alzheimers disease</t>
+          <t>bipolar disorder + schizophrenia + alzheimers disease + depression</t>
         </is>
       </c>
       <c r="W7" t="inlineStr"/>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ukbb + ros/map + dbgap + phs001672.v1.p1 + adsp</t>
+          <t>dbgap + phs001672.v1.p1 + ukbb + adsp + ros/map</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1427,19 +1427,19 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1000g + 1000 genomes phase 3 + topmed</t>
+          <t>1000 genomes phase 3 + 1000g + topmed</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>european ancestry + aa + eur</t>
+          <t>eur + european ancestry + aa</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>depression + bipolar disorder + schizophrenia + alzheimers disease</t>
+          <t>bipolar disorder + schizophrenia + alzheimers disease + depression</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ukbb + ros/map + dbgap + phs001672.v1.p1 + adsp</t>
+          <t>dbgap + phs001672.v1.p1 + ukbb + adsp + ros/map</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1546,19 +1546,19 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1000g + 1000 genomes phase 3 + topmed</t>
+          <t>1000 genomes phase 3 + 1000g + topmed</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>european ancestry + aa + eur</t>
+          <t>eur + european ancestry + aa</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>depression + bipolar disorder + schizophrenia + alzheimers disease</t>
+          <t>bipolar disorder + schizophrenia + alzheimers disease + depression</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ukbb + ros/map + dbgap + phs001672.v1.p1 + adsp</t>
+          <t>dbgap + phs001672.v1.p1 + ukbb + adsp + ros/map</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1665,19 +1665,19 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1000g + 1000 genomes phase 3 + topmed</t>
+          <t>1000 genomes phase 3 + 1000g + topmed</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>european ancestry + aa + eur</t>
+          <t>eur + european ancestry + aa</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>depression + bipolar disorder + schizophrenia + alzheimers disease</t>
+          <t>bipolar disorder + schizophrenia + alzheimers disease + depression</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ukbb + ros/map + dbgap + phs001672.v1.p1 + adsp</t>
+          <t>dbgap + phs001672.v1.p1 + ukbb + adsp + ros/map</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -1784,19 +1784,19 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1000g + 1000 genomes phase 3 + topmed</t>
+          <t>1000 genomes phase 3 + 1000g + topmed</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>european ancestry + aa + eur</t>
+          <t>eur + european ancestry + aa</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>depression + bipolar disorder + schizophrenia + alzheimers disease</t>
+          <t>bipolar disorder + schizophrenia + alzheimers disease + depression</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ukbb + ros/map + dbgap + phs001672.v1.p1 + adsp</t>
+          <t>dbgap + phs001672.v1.p1 + ukbb + adsp + ros/map</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1903,19 +1903,19 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1000g + 1000 genomes phase 3 + topmed</t>
+          <t>1000 genomes phase 3 + 1000g + topmed</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>european ancestry + aa + eur</t>
+          <t>eur + european ancestry + aa</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>depression + bipolar disorder + schizophrenia + alzheimers disease</t>
+          <t>bipolar disorder + schizophrenia + alzheimers disease + depression</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ukbb + ros/map + dbgap + phs001672.v1.p1 + adsp</t>
+          <t>dbgap + phs001672.v1.p1 + ukbb + adsp + ros/map</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -2022,19 +2022,19 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1000g + 1000 genomes phase 3 + topmed</t>
+          <t>1000 genomes phase 3 + 1000g + topmed</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>european ancestry + aa + eur</t>
+          <t>eur + european ancestry + aa</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>depression + bipolar disorder + schizophrenia + alzheimers disease</t>
+          <t>bipolar disorder + schizophrenia + alzheimers disease + depression</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ukbb + ros/map + dbgap + phs001672.v1.p1 + adsp</t>
+          <t>dbgap + phs001672.v1.p1 + ukbb + adsp + ros/map</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -2141,19 +2141,19 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1000g + 1000 genomes phase 3 + topmed</t>
+          <t>1000 genomes phase 3 + 1000g + topmed</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>european ancestry + aa + eur</t>
+          <t>eur + european ancestry + aa</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>depression + bipolar disorder + schizophrenia + alzheimers disease</t>
+          <t>bipolar disorder + schizophrenia + alzheimers disease + depression</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ukbb + ros/map + dbgap + phs001672.v1.p1 + adsp</t>
+          <t>dbgap + phs001672.v1.p1 + ukbb + adsp + ros/map</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -2260,19 +2260,19 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1000g + 1000 genomes phase 3 + topmed</t>
+          <t>1000 genomes phase 3 + 1000g + topmed</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>european ancestry + aa + eur</t>
+          <t>eur + european ancestry + aa</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>depression + bipolar disorder + schizophrenia + alzheimers disease</t>
+          <t>bipolar disorder + schizophrenia + alzheimers disease + depression</t>
         </is>
       </c>
       <c r="W15" t="inlineStr"/>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ukbb + ros/map + dbgap + phs001672.v1.p1 + adsp</t>
+          <t>dbgap + phs001672.v1.p1 + ukbb + adsp + ros/map</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -2379,19 +2379,19 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1000g + 1000 genomes phase 3 + topmed</t>
+          <t>1000 genomes phase 3 + 1000g + topmed</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>european ancestry + aa + eur</t>
+          <t>eur + european ancestry + aa</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>depression + bipolar disorder + schizophrenia + alzheimers disease</t>
+          <t>bipolar disorder + schizophrenia + alzheimers disease + depression</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
